--- a/src/test/resources/ImportFile/Catagories1.xlsx
+++ b/src/test/resources/ImportFile/Catagories1.xlsx
@@ -5,22 +5,27 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\ZlaataQAsever0\src\test\resources\ImportFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64080606-8D45-4E15-A257-0EFFC0D9A2A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306D8FA-BE2A-4255-816C-A88B6EA06434}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>S.No</t>
   </si>
@@ -28,6 +33,9 @@
     <t>Menu Name</t>
   </si>
   <si>
+    <t>Brand Type</t>
+  </si>
+  <si>
     <t>Products</t>
   </si>
   <si>
@@ -85,59 +93,59 @@
     <t>Updated At</t>
   </si>
   <si>
+    <t>Zlaata India</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>https://zlaata.s3.ap-south-1.amazonaws.com/Banner/5510c5e2-c556-483d-ab11-5b99bd46558e.jpeg</t>
+  </si>
+  <si>
+    <t>https://zlaata.s3.ap-south-1.amazonaws.com/Banner/b7573fe4-dbc6-457c-9552-3a5afff2a547.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dqkmypqmb/image/upload/v1743054851/gnjn01pmvb6s2otthex1.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dqkmypqmb/image/upload/v1743054853/j89zbojzphfei6ntxy5e.jpg</t>
+  </si>
+  <si>
+    <t>4 Jan 2025, 12:15</t>
+  </si>
+  <si>
+    <t>27 Mar 2025, 11:35</t>
+  </si>
+  <si>
     <t>Shop</t>
   </si>
   <si>
-    <t>ABCD, Kurta Pant With Dupatta 1, Kurta Pant With Dupatta 2, Kurta Pant With Dupatta 3, Kurta Pant With Dupatta 4, Kurta Pant With Dupatta 5, Kurta Pant With Dupatta 7</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>https://zlaata.s3.ap-south-1.amazonaws.com/Banner/5510c5e2-c556-483d-ab11-5b99bd46558e.jpeg</t>
-  </si>
-  <si>
-    <t>https://zlaata.s3.ap-south-1.amazonaws.com/Banner/b7573fe4-dbc6-457c-9552-3a5afff2a547.webp</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dqkmypqmb/image/upload/v1743054851/gnjn01pmvb6s2otthex1.jpg</t>
-  </si>
-  <si>
-    <t>https://res.cloudinary.com/dqkmypqmb/image/upload/v1743054853/j89zbojzphfei6ntxy5e.jpg</t>
-  </si>
-  <si>
-    <t>4 Jan 2025, 12:15</t>
-  </si>
-  <si>
-    <t>27 Mar 2025, 11:35</t>
-  </si>
-  <si>
-    <t>Auto123</t>
+    <t>Automation1</t>
+  </si>
+  <si>
+    <t>Janasya Women's Dark Green Rayon,Printed Shrug,super dress</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,9 +169,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,10 +488,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="39.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,70 +558,77 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" ht="405.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="202.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="2">
+        <v>33</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="2">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="S2" s="2">
-        <v>1</v>
-      </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="2">
+        <v>10</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>